--- a/Robocar_Testauswertung.xlsx
+++ b/Robocar_Testauswertung.xlsx
@@ -5,17 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lukas\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lukas\Desktop\Hochschule\Informatik_1_DHBW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0383D695-0F34-46D8-92CB-A56DB00F3B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6262B1AD-0D3D-46FF-8F71-142A9F448A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="2970" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="2970" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Anleitung" sheetId="1" r:id="rId1"/>
-    <sheet name="Messdaten" sheetId="2" r:id="rId2"/>
-    <sheet name="Auswertung" sheetId="3" r:id="rId3"/>
+    <sheet name="Messdaten" sheetId="2" r:id="rId1"/>
+    <sheet name="Auswertung" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,37 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="163">
-  <si>
-    <t>Robocar Testauswertung – PID / Fahrparameter</t>
-  </si>
-  <si>
-    <t>Pro Einstellung 4 Läufe messen, Mittelwert vergleichen und die beste Kombination finden.</t>
-  </si>
-  <si>
-    <t>So benutzt ihr die Datei:</t>
-  </si>
-  <si>
-    <t>1) In Messdaten pro Zeile genau eine Parameterkombination eintragen.</t>
-  </si>
-  <si>
-    <t>2) Zeit_1_s bis Zeit_4_s mit den 4 gemessenen Zeiten füllen.</t>
-  </si>
-  <si>
-    <t>3) Mittelwert, Standardabweichung, Best- und Schlechtestzeit werden automatisch berechnet.</t>
-  </si>
-  <si>
-    <t>4) In Auswertung seht ihr die 10 schnellsten Versuche.</t>
-  </si>
-  <si>
-    <t>5) Der Graph zeigt die besten Einstellungen nach Mittelwert.</t>
-  </si>
-  <si>
-    <t>6) Leere Zeilen werden ignoriert.</t>
-  </si>
-  <si>
-    <t>Hinweis: Bei gleichen Zeiten sorgt eine Hilfsspalte für eine stabile Reihenfolge.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="153">
   <si>
     <t>Test_ID</t>
   </si>
@@ -1087,101 +1056,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="95" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="11" customHeight="1">
-      <c r="A1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-    </row>
-    <row r="2" spans="1:8" ht="11" customHeight="1"/>
-    <row r="3" spans="1:8" ht="11" customHeight="1">
-      <c r="A3" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-    </row>
-    <row r="4" spans="1:8" ht="11" customHeight="1"/>
-    <row r="5" spans="1:8" ht="11" customHeight="1">
-      <c r="A5" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="11" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="11" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="11" customHeight="1">
-      <c r="A8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="11" customHeight="1">
-      <c r="A9" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="11" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="11" customHeight="1">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="11" customHeight="1">
-      <c r="A12" s="1"/>
-    </row>
-    <row r="13" spans="1:8" ht="11" customHeight="1">
-      <c r="A13" s="1"/>
-    </row>
-    <row r="14" spans="1:8" ht="11" customHeight="1">
-      <c r="A14" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="11" customHeight="1"/>
-    <row r="16" spans="1:8" ht="11" customHeight="1"/>
-    <row r="17" ht="11" customHeight="1"/>
-    <row r="18" ht="11" customHeight="1"/>
-    <row r="19" ht="11" customHeight="1"/>
-    <row r="20" ht="11" customHeight="1"/>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A3:H3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A4:V104"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13.5"/>
@@ -1204,75 +1078,75 @@
   <sheetData>
     <row r="4" spans="1:22" ht="27.75">
       <c r="A4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="P4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="Q4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="R4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="U4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="V4" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="V4" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B5" s="4">
         <v>34</v>
@@ -1327,10 +1201,10 @@
         <v>16</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="T5" s="4">
         <v>5</v>
@@ -1343,7 +1217,7 @@
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B6" s="4">
         <v>35</v>
@@ -1398,16 +1272,16 @@
         <v>10</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="T6" s="4">
         <v>10</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="V6" s="5">
         <f t="shared" si="3"/>
@@ -1416,7 +1290,7 @@
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B7" s="4">
         <v>37</v>
@@ -1471,16 +1345,16 @@
         <v>10</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="T7" s="4">
         <v>10</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="V7" s="5">
         <f t="shared" si="3"/>
@@ -1489,7 +1363,7 @@
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B8" s="4">
         <v>32.1</v>
@@ -1544,10 +1418,10 @@
         <v>10</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="T8" s="4">
         <v>10</v>
@@ -1560,7 +1434,7 @@
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B9" s="4">
         <v>32.799999999999997</v>
@@ -1611,16 +1485,16 @@
         <v>12</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="T9" s="4">
         <v>5</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="V9" s="5">
         <f t="shared" si="3"/>
@@ -1629,10 +1503,10 @@
     </row>
     <row r="10" spans="1:22" ht="27">
       <c r="A10" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -1664,10 +1538,10 @@
       <c r="R10" s="4"/>
       <c r="S10" s="4"/>
       <c r="T10" s="4" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="V10" s="5" t="str">
         <f t="shared" si="3"/>
@@ -1676,7 +1550,7 @@
     </row>
     <row r="11" spans="1:22" ht="54">
       <c r="A11" s="1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B11" s="4">
         <v>29.8</v>
@@ -1716,7 +1590,7 @@
         <v>45</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="N11" s="4">
         <v>10</v>
@@ -1731,16 +1605,16 @@
         <v>12</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="T11" s="4">
         <v>8</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="V11" s="5">
         <f t="shared" si="3"/>
@@ -1749,7 +1623,7 @@
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="B12" s="4">
         <v>31</v>
@@ -1789,7 +1663,7 @@
         <v>45</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="N12" s="4">
         <v>8</v>
@@ -1804,10 +1678,10 @@
         <v>12</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="T12" s="4">
         <v>8</v>
@@ -1820,7 +1694,7 @@
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B13" s="4">
         <v>27</v>
@@ -1860,7 +1734,7 @@
         <v>45</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="N13" s="4">
         <v>8</v>
@@ -1875,10 +1749,10 @@
         <v>12</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="T13" s="4">
         <v>8</v>
@@ -1891,7 +1765,7 @@
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B14" s="4">
         <v>28</v>
@@ -1931,7 +1805,7 @@
         <v>42</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="N14" s="4">
         <v>8</v>
@@ -1946,10 +1820,10 @@
         <v>12</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="S14" s="4" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="T14" s="4">
         <v>8</v>
@@ -1962,7 +1836,7 @@
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B15" s="4">
         <v>27</v>
@@ -2002,7 +1876,7 @@
         <v>42</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="N15" s="4">
         <v>8</v>
@@ -2017,16 +1891,16 @@
         <v>12</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="S15" s="4" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="T15" s="4">
         <v>8</v>
       </c>
       <c r="U15" s="3" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="V15" s="5">
         <f t="shared" si="3"/>
@@ -2035,7 +1909,7 @@
     </row>
     <row r="16" spans="1:22" ht="27">
       <c r="A16" s="1" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B16" s="4">
         <v>28.6</v>
@@ -2075,7 +1949,7 @@
         <v>45</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="N16" s="4">
         <v>8</v>
@@ -2090,25 +1964,25 @@
         <v>12</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="T16" s="4">
         <v>8</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="V16" s="5">
         <f t="shared" si="3"/>
         <v>29.425160000000002</v>
       </c>
     </row>
-    <row r="17" spans="1:22" ht="27">
+    <row r="17" spans="1:22">
       <c r="A17" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B17" s="4">
         <v>28</v>
@@ -2148,7 +2022,7 @@
         <v>45</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="N17" s="4">
         <v>8</v>
@@ -2163,16 +2037,16 @@
         <v>12</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="T17" s="4">
         <v>8</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="V17" s="5">
         <f t="shared" si="3"/>
@@ -2181,7 +2055,7 @@
     </row>
     <row r="18" spans="1:22" ht="40.5">
       <c r="A18" s="1" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B18" s="4">
         <v>26.4</v>
@@ -2221,7 +2095,7 @@
         <v>45</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="N18" s="4">
         <v>8</v>
@@ -2236,16 +2110,16 @@
         <v>12</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="T18" s="4">
         <v>8</v>
       </c>
       <c r="U18" s="3" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="V18" s="5">
         <f t="shared" si="3"/>
@@ -2254,7 +2128,7 @@
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -2295,7 +2169,7 @@
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -2336,7 +2210,7 @@
     </row>
     <row r="21" spans="1:22">
       <c r="A21" s="1" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -2377,7 +2251,7 @@
     </row>
     <row r="22" spans="1:22">
       <c r="A22" s="1" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -2418,7 +2292,7 @@
     </row>
     <row r="23" spans="1:22">
       <c r="A23" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -2459,7 +2333,7 @@
     </row>
     <row r="24" spans="1:22">
       <c r="A24" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -2500,7 +2374,7 @@
     </row>
     <row r="25" spans="1:22">
       <c r="A25" s="1" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -2541,7 +2415,7 @@
     </row>
     <row r="26" spans="1:22">
       <c r="A26" s="1" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -2582,7 +2456,7 @@
     </row>
     <row r="27" spans="1:22">
       <c r="A27" s="1" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -2623,7 +2497,7 @@
     </row>
     <row r="28" spans="1:22">
       <c r="A28" s="1" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -2664,7 +2538,7 @@
     </row>
     <row r="29" spans="1:22">
       <c r="A29" s="1" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -2705,7 +2579,7 @@
     </row>
     <row r="30" spans="1:22">
       <c r="A30" s="1" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -2746,7 +2620,7 @@
     </row>
     <row r="31" spans="1:22">
       <c r="A31" s="1" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -2787,7 +2661,7 @@
     </row>
     <row r="32" spans="1:22">
       <c r="A32" s="1" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -2828,7 +2702,7 @@
     </row>
     <row r="33" spans="1:22">
       <c r="A33" s="1" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -2869,7 +2743,7 @@
     </row>
     <row r="34" spans="1:22">
       <c r="A34" s="1" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -2910,7 +2784,7 @@
     </row>
     <row r="35" spans="1:22">
       <c r="A35" s="1" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -2951,7 +2825,7 @@
     </row>
     <row r="36" spans="1:22">
       <c r="A36" s="1" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -2992,7 +2866,7 @@
     </row>
     <row r="37" spans="1:22">
       <c r="A37" s="1" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -3033,7 +2907,7 @@
     </row>
     <row r="38" spans="1:22">
       <c r="A38" s="1" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -3074,7 +2948,7 @@
     </row>
     <row r="39" spans="1:22">
       <c r="A39" s="1" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -3115,7 +2989,7 @@
     </row>
     <row r="40" spans="1:22">
       <c r="A40" s="1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -3156,7 +3030,7 @@
     </row>
     <row r="41" spans="1:22">
       <c r="A41" s="1" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -3197,7 +3071,7 @@
     </row>
     <row r="42" spans="1:22">
       <c r="A42" s="1" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -3238,7 +3112,7 @@
     </row>
     <row r="43" spans="1:22">
       <c r="A43" s="1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -3279,7 +3153,7 @@
     </row>
     <row r="44" spans="1:22">
       <c r="A44" s="1" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -3320,7 +3194,7 @@
     </row>
     <row r="45" spans="1:22">
       <c r="A45" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -3361,7 +3235,7 @@
     </row>
     <row r="46" spans="1:22">
       <c r="A46" s="1" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -3402,7 +3276,7 @@
     </row>
     <row r="47" spans="1:22">
       <c r="A47" s="1" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -3443,7 +3317,7 @@
     </row>
     <row r="48" spans="1:22">
       <c r="A48" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -3484,7 +3358,7 @@
     </row>
     <row r="49" spans="1:22">
       <c r="A49" s="1" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -3525,7 +3399,7 @@
     </row>
     <row r="50" spans="1:22">
       <c r="A50" s="1" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -3566,7 +3440,7 @@
     </row>
     <row r="51" spans="1:22">
       <c r="A51" s="1" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -3607,7 +3481,7 @@
     </row>
     <row r="52" spans="1:22">
       <c r="A52" s="1" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -3648,7 +3522,7 @@
     </row>
     <row r="53" spans="1:22">
       <c r="A53" s="1" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -3689,7 +3563,7 @@
     </row>
     <row r="54" spans="1:22">
       <c r="A54" s="1" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -3730,7 +3604,7 @@
     </row>
     <row r="55" spans="1:22">
       <c r="A55" s="1" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -3771,7 +3645,7 @@
     </row>
     <row r="56" spans="1:22">
       <c r="A56" s="1" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -3812,7 +3686,7 @@
     </row>
     <row r="57" spans="1:22">
       <c r="A57" s="1" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -3853,7 +3727,7 @@
     </row>
     <row r="58" spans="1:22">
       <c r="A58" s="1" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -3894,7 +3768,7 @@
     </row>
     <row r="59" spans="1:22">
       <c r="A59" s="1" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -3935,7 +3809,7 @@
     </row>
     <row r="60" spans="1:22">
       <c r="A60" s="1" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -3976,7 +3850,7 @@
     </row>
     <row r="61" spans="1:22">
       <c r="A61" s="1" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -4017,7 +3891,7 @@
     </row>
     <row r="62" spans="1:22">
       <c r="A62" s="1" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -4058,7 +3932,7 @@
     </row>
     <row r="63" spans="1:22">
       <c r="A63" s="1" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -4099,7 +3973,7 @@
     </row>
     <row r="64" spans="1:22">
       <c r="A64" s="1" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -4140,7 +4014,7 @@
     </row>
     <row r="65" spans="1:22">
       <c r="A65" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -4181,7 +4055,7 @@
     </row>
     <row r="66" spans="1:22">
       <c r="A66" s="1" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -4222,7 +4096,7 @@
     </row>
     <row r="67" spans="1:22">
       <c r="A67" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -4263,7 +4137,7 @@
     </row>
     <row r="68" spans="1:22">
       <c r="A68" s="1" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -4304,7 +4178,7 @@
     </row>
     <row r="69" spans="1:22">
       <c r="A69" s="1" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -4345,7 +4219,7 @@
     </row>
     <row r="70" spans="1:22">
       <c r="A70" s="1" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -4386,7 +4260,7 @@
     </row>
     <row r="71" spans="1:22">
       <c r="A71" s="1" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -4427,7 +4301,7 @@
     </row>
     <row r="72" spans="1:22">
       <c r="A72" s="1" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -4468,7 +4342,7 @@
     </row>
     <row r="73" spans="1:22">
       <c r="A73" s="1" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -4509,7 +4383,7 @@
     </row>
     <row r="74" spans="1:22">
       <c r="A74" s="1" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -4550,7 +4424,7 @@
     </row>
     <row r="75" spans="1:22">
       <c r="A75" s="1" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -4591,7 +4465,7 @@
     </row>
     <row r="76" spans="1:22">
       <c r="A76" s="1" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -4632,7 +4506,7 @@
     </row>
     <row r="77" spans="1:22">
       <c r="A77" s="1" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -4673,7 +4547,7 @@
     </row>
     <row r="78" spans="1:22">
       <c r="A78" s="1" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -4714,7 +4588,7 @@
     </row>
     <row r="79" spans="1:22">
       <c r="A79" s="1" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -4755,7 +4629,7 @@
     </row>
     <row r="80" spans="1:22">
       <c r="A80" s="1" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -4796,7 +4670,7 @@
     </row>
     <row r="81" spans="1:22">
       <c r="A81" s="1" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -4837,7 +4711,7 @@
     </row>
     <row r="82" spans="1:22">
       <c r="A82" s="1" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -4878,7 +4752,7 @@
     </row>
     <row r="83" spans="1:22">
       <c r="A83" s="1" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -4919,7 +4793,7 @@
     </row>
     <row r="84" spans="1:22">
       <c r="A84" s="1" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -4960,7 +4834,7 @@
     </row>
     <row r="85" spans="1:22">
       <c r="A85" s="1" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -5001,7 +4875,7 @@
     </row>
     <row r="86" spans="1:22">
       <c r="A86" s="1" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
@@ -5042,7 +4916,7 @@
     </row>
     <row r="87" spans="1:22">
       <c r="A87" s="1" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
@@ -5083,7 +4957,7 @@
     </row>
     <row r="88" spans="1:22">
       <c r="A88" s="1" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -5124,7 +4998,7 @@
     </row>
     <row r="89" spans="1:22">
       <c r="A89" s="1" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
@@ -5165,7 +5039,7 @@
     </row>
     <row r="90" spans="1:22">
       <c r="A90" s="1" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -5206,7 +5080,7 @@
     </row>
     <row r="91" spans="1:22">
       <c r="A91" s="1" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -5247,7 +5121,7 @@
     </row>
     <row r="92" spans="1:22">
       <c r="A92" s="1" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -5288,7 +5162,7 @@
     </row>
     <row r="93" spans="1:22">
       <c r="A93" s="1" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -5329,7 +5203,7 @@
     </row>
     <row r="94" spans="1:22">
       <c r="A94" s="1" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -5370,7 +5244,7 @@
     </row>
     <row r="95" spans="1:22">
       <c r="A95" s="1" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -5411,7 +5285,7 @@
     </row>
     <row r="96" spans="1:22">
       <c r="A96" s="1" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -5452,7 +5326,7 @@
     </row>
     <row r="97" spans="1:22">
       <c r="A97" s="1" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -5493,7 +5367,7 @@
     </row>
     <row r="98" spans="1:22">
       <c r="A98" s="1" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -5534,7 +5408,7 @@
     </row>
     <row r="99" spans="1:22">
       <c r="A99" s="1" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -5575,7 +5449,7 @@
     </row>
     <row r="100" spans="1:22">
       <c r="A100" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -5616,14 +5490,14 @@
     </row>
     <row r="101" spans="1:22">
       <c r="A101" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
       <c r="F101" s="5" t="str">
-        <f t="shared" ref="F101:F132" si="13">IF(COUNT(B101:E101)=0,"",AVERAGE(B101:E101))</f>
+        <f t="shared" ref="F101:F104" si="13">IF(COUNT(B101:E101)=0,"",AVERAGE(B101:E101))</f>
         <v/>
       </c>
       <c r="G101" s="5" t="str">
@@ -5657,7 +5531,7 @@
     </row>
     <row r="102" spans="1:22">
       <c r="A102" s="1" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -5698,7 +5572,7 @@
     </row>
     <row r="103" spans="1:22">
       <c r="A103" s="1" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -5739,7 +5613,7 @@
     </row>
     <row r="104" spans="1:22">
       <c r="A104" s="1" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -5836,7 +5710,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13.5"/>
@@ -5857,101 +5731,101 @@
   <sheetData>
     <row r="1" spans="1:15" ht="12" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="O1" s="11" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="13.9">
       <c r="A3" s="12" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="L3" s="12" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="N3" s="12" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="O3" s="12" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="6" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B5" s="8">
         <f>IF(COUNT(Messdaten!$F$5:$F$104)=0,"",MIN(Messdaten!$F$5:$F$104))</f>
@@ -5960,7 +5834,7 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="6" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="B6" s="8" t="str">
         <f>IF(COUNT(Messdaten!$F$5:$F$104)=0,"",INDEX(Messdaten!$A$5:$A$104,MATCH(SMALL(Messdaten!$V$5:$V$104,1),Messdaten!$V$5:$V$104,0)))</f>
@@ -5969,7 +5843,7 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="6" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="B7" s="10">
         <f>COUNT(Messdaten!$F$5:$F$104)</f>
@@ -5978,7 +5852,7 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="6" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="B8" s="8">
         <f>IF(COUNT(Messdaten!$F$5:$F$104)=0,"",MAX(Messdaten!$F$5:$F$104))</f>
@@ -5987,49 +5861,49 @@
     </row>
     <row r="11" spans="1:15" ht="18" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C11" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="I11" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M11" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="N11" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="O11" s="7" t="s">
         <v>17</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L11" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="N11" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="O11" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:15">
